--- a/results/momentum_strong_2026-08-22.xlsx
+++ b/results/momentum_strong_2026-08-22.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADPT</t>
+          <t>ADAMK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEI</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AEI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>AESP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AIRO</t>
+          <t>AEYE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>AIFA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALOT</t>
+          <t>AIRO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AIXC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>ALOT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>ALPX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ANL</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APLM</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>ANGX</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AQST</t>
+          <t>APLM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>APPF</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARCC</t>
+          <t>APPN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AREC</t>
+          <t>AQST</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARX</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>AREC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>ARX</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ASRV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>ATKR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1090,13 +1090,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AUTL</t>
+          <t>ATRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PRHIZ</t>
+          <t>PUSA</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1108,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>SHMD</t>
         </is>
       </c>
     </row>
@@ -1126,13 +1126,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>SKHY</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AVR</t>
+          <t>AUTL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AVTR</t>
+          <t>AVO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BCDA</t>
+          <t>AVR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>AVTR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1225,12 +1225,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BETA</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1239,12 +1239,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNTX</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BGDE</t>
+          <t>BCDA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1253,12 +1253,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BPYPP</t>
+          <t>BNTX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1267,12 +1267,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BRNX</t>
+          <t>BPYPP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>BETA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRZE</t>
+          <t>BRNX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BOLD</t>
+          <t>BGDE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1295,12 +1295,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>BLKB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1309,12 +1309,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BPYPO</t>
+          <t>BNTC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BOLD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1337,12 +1337,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BULLW</t>
+          <t>BTGO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BPRN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1351,12 +1351,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BWB</t>
+          <t>BULLW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BPYPO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1365,12 +1365,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BWB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BSY</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BTU</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1393,12 +1393,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1407,12 +1407,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CDLR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1421,12 +1421,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BYND</t>
+          <t>BTU</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1435,12 +1435,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CGAU</t>
+          <t>CEPO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CAKE</t>
+          <t>BVC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>CGAU</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CCC</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1463,12 +1463,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CHTRP</t>
+          <t>CHDN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1477,12 +1477,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>CHTRP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CCG</t>
+          <t>CAKE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1491,12 +1491,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CITR</t>
+          <t>CING</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>CCC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1505,12 +1505,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CITR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1519,12 +1519,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CMMB</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CETY</t>
+          <t>CCG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1533,12 +1533,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CMTV</t>
+          <t>CMMB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1547,12 +1547,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CNOBP</t>
+          <t>CMTV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1561,12 +1561,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>CNOBP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CLBK</t>
+          <t>CETY</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COCP</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>CHCI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1589,12 +1589,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>COCP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>CHNR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1603,12 +1603,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CSHR</t>
+          <t>CRBP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CLBK</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1617,12 +1617,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>CSHR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1631,12 +1631,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>CSTL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CMPS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1645,12 +1645,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CTRM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CPB</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CTRM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CPBI</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1673,12 +1673,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CYCN</t>
+          <t>CVSA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CRMD</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1687,12 +1687,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CYCN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1701,12 +1701,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CYPH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CPBI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CYRX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>CRMD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1729,12 +1729,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CZFS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1743,12 +1743,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>DCBO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CRVL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1757,12 +1757,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CSAI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1771,12 +1771,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CTW</t>
+          <t>CSWC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1785,12 +1785,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>DFDV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1799,12 +1799,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>DHCNI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DAAQ</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1813,12 +1813,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>DMAA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>CTW</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1827,12 +1827,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>DMLP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DBX</t>
+          <t>CZNC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1841,12 +1841,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DRTS</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DERM</t>
+          <t>DAAQ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1855,12 +1855,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>DRTS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DFTX</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1869,12 +1869,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DSGN</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>DBX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>DSGN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DNUT</t>
+          <t>DERM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1897,12 +1897,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>DTCX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DUOT</t>
+          <t>DFTX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1911,12 +1911,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DWTX</t>
+          <t>DTIL</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1925,12 +1925,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EDRY</t>
+          <t>DWTX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>DNUT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1939,12 +1939,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>EDRY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DSC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1953,12 +1953,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>ELBM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EGHA</t>
+          <t>DUOT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1967,12 +1967,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>ELLA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1981,12 +1981,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ELVN</t>
+          <t>ECCU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1995,12 +1995,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>ELOX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EROK</t>
+          <t>EFOR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2009,12 +2009,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>ENTX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EGHA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2023,12 +2023,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>ELE</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2037,12 +2037,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EXLS</t>
+          <t>ELVN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>EROK</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2065,12 +2065,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBRX</t>
+          <t>EXPO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FDMT</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2079,12 +2079,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FHTX</t>
+          <t>FBLG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>EXFY</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2093,12 +2093,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>FBRX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FENC</t>
+          <t>EXLS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2107,12 +2107,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>FHTX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>FCBC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2121,12 +2121,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FLNT</t>
+          <t>FIVE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FIGR</t>
+          <t>FDMT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2135,12 +2135,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>FIZZ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FIVN</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2149,12 +2149,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FLNT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>FENC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2163,12 +2163,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>FLYW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>FERA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2177,12 +2177,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FTH</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>FIGR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2191,12 +2191,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FUTU</t>
+          <t>FTDR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>FIVN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2205,12 +2205,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>FTH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FOXF</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2219,12 +2219,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>FUTU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>FNKO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2233,12 +2233,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>FVN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>FORR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2247,12 +2247,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FWONA</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2261,12 +2261,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>GAINZ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>FOXF</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2275,12 +2275,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>GECCI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>FRNM</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2289,12 +2289,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>GIBO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2303,12 +2303,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>GOLD</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>FWONA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2317,12 +2317,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GECCG</t>
+          <t>FWONK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2331,12 +2331,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HLXC</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>GAME</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2345,12 +2345,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HOLO</t>
+          <t>HELP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>GCBC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2359,12 +2359,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>HQI</t>
+          <t>HLXC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GLBS</t>
+          <t>GDYN</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2373,12 +2373,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>HOLO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GMRS</t>
+          <t>GECCG</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2387,12 +2387,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HYPD</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2401,12 +2401,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>HYNE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2415,12 +2415,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>HYPD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>GLBS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2429,12 +2429,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>GMRS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2443,12 +2443,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>IDYA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GRRR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2457,12 +2457,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GRVY</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2471,12 +2471,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>INMB</t>
+          <t>IMPP</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GSHD</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2485,12 +2485,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GTEC</t>
+          <t>GROW</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2499,12 +2499,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>INMB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GTIM</t>
+          <t>GRRR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>GRVY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2527,12 +2527,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JATT</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>GSHD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2541,12 +2541,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JUNS</t>
+          <t>IVVD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GTEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2555,12 +2555,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>JATT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>HLNE</t>
+          <t>GTIM</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2569,12 +2569,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>JUNS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HNST</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2583,12 +2583,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>LGVN</t>
+          <t>KRT</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2597,12 +2597,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LOT</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2611,12 +2611,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>LGVN</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HRZN</t>
+          <t>HLNE</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2625,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>LOT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>HNST</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2639,12 +2639,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>MANH</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HUDI</t>
+          <t>HPK</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2653,12 +2653,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>MCAH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HURC</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2667,12 +2667,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>MCRI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>IACO</t>
+          <t>HRZN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2681,12 +2681,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>MEDP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>HTFL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2695,12 +2695,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MRDN</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>HUDI</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2709,12 +2709,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>MFIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>IMUX</t>
+          <t>HURC</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2723,12 +2723,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSBIP</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>IACO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2737,12 +2737,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>MRDN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>INDI</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2751,12 +2751,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NBP</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>INO</t>
+          <t>IMCR</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2765,12 +2765,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NCI</t>
+          <t>MSBIP</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IPHA</t>
+          <t>IMMX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2779,12 +2779,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>NAKA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>IMUX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>NBP</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2807,12 +2807,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>NCI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>INDI</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2821,12 +2821,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>INO</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2835,12 +2835,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NTRB</t>
+          <t>NMFCZ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>IPHA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2849,12 +2849,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>NRC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>JAN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NVCT</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>KMDA</t>
+          <t>JFU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2877,12 +2877,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ODTX</t>
+          <t>NTRB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KOPN</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2891,12 +2891,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OMEX</t>
+          <t>NVAX</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>KPRX</t>
+          <t>JOYY</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2905,12 +2905,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ONBPO</t>
+          <t>NVCT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>KRKR</t>
+          <t>KELYA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2919,12 +2919,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORBS</t>
+          <t>OCAC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KRNY</t>
+          <t>KLTR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2933,12 +2933,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OTLY</t>
+          <t>ODTX</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2947,12 +2947,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>OMEX</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2961,12 +2961,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ONBPO</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KZIA</t>
+          <t>KPRX</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2975,12 +2975,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>KRKR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2989,12 +2989,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PANL</t>
+          <t>OTLY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>KRNY</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3003,12 +3003,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>OVLY</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LEXX</t>
+          <t>KSPI</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3017,12 +3017,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>KWY</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3031,12 +3031,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>KZIA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3045,12 +3045,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PFX</t>
+          <t>PANL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3059,12 +3059,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PAYS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>LSE</t>
+          <t>LEGH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3073,12 +3073,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>PBLS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>LYFT</t>
+          <t>LEXX</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3087,12 +3087,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PRZO</t>
+          <t>PEBK</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MAKO</t>
+          <t>LIFE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3101,12 +3101,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PSEC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>LMRI</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3115,12 +3115,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PSNL</t>
+          <t>PFX</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MBINL</t>
+          <t>LPTH</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3129,12 +3129,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PHOS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MCFT</t>
+          <t>LSE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3143,12 +3143,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PURR</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>LTGO</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3157,12 +3157,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>PRGS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>LYFT</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3171,12 +3171,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>PRZO</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MGTX</t>
+          <t>MAKO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3185,12 +3185,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RDI</t>
+          <t>PSEC</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MASS</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3199,12 +3199,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>PSNL</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>MBINL</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3213,12 +3213,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>REFI</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>MCFT</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -3227,12 +3227,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>PURR</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -3241,12 +3241,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MMED</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -3255,12 +3255,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>PYPD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MNKD</t>
+          <t>MGTX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -3269,12 +3269,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>RDI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MNOV</t>
+          <t>MGYR</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -3283,12 +3283,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RMNI</t>
+          <t>REAX</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MOLN</t>
+          <t>MICC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -3297,12 +3297,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RMR</t>
+          <t>REFI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MRX</t>
+          <t>MINE</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -3311,12 +3311,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RNAC</t>
+          <t>RENT</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>MLAB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -3325,12 +3325,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>RGEN</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MYSE</t>
+          <t>MMED</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -3339,12 +3339,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RVMD</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MYSZ</t>
+          <t>MNKD</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -3353,12 +3353,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>RMBI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>MNOV</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -3367,12 +3367,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>RMNI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MOLN</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -3381,12 +3381,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>RMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>MRX</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -3395,12 +3395,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>RNAC</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NIPG</t>
+          <t>MTEX</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -3409,12 +3409,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>MYSE</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -3423,12 +3423,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>MYSZ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -3437,12 +3437,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>SATA</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>NAVI</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -3451,12 +3451,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>NTHI</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -3465,12 +3465,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SLS</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>NICM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -3479,12 +3479,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SMJF</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NIPG</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -3493,12 +3493,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NIQ</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -3507,12 +3507,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SHIP</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>NPAC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -3521,12 +3521,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SRTA</t>
+          <t>SIBN</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>NSIT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -3535,12 +3535,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SSNC</t>
+          <t>SIND</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OBIO</t>
+          <t>NTHI</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -3549,12 +3549,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>SLDE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>OCCI</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -3563,12 +3563,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>SLS</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>OCUL</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -3577,12 +3577,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>SMJF</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -3591,12 +3591,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>SMTI</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>OGC</t>
+          <t>NXPL</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -3605,12 +3605,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>OGG</t>
+          <t>OABI</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -3619,12 +3619,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>SRTA</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>OGI</t>
+          <t>OBIO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -3633,12 +3633,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>SSMR</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OMER</t>
+          <t>OCCI</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -3647,12 +3647,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TBPH</t>
+          <t>SSNC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OMSE</t>
+          <t>OCUL</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -3661,12 +3661,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TCBX</t>
+          <t>SSRM</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OXLCG</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -3675,12 +3675,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>OGC</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -3689,12 +3689,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TII</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>OGG</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -3703,12 +3703,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PBAM</t>
+          <t>OGI</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -3717,12 +3717,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>OMER</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -3731,12 +3731,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SYRE</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>OMSE</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -3745,12 +3745,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>TAYD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>OXLCG</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -3759,12 +3759,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>TBPH</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PHOE</t>
+          <t>OXLCM</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -3773,12 +3773,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>TCBX</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -3787,12 +3787,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VGNT</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PMN</t>
+          <t>PBAM</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -3801,12 +3801,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VMET</t>
+          <t>TII</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>PBM</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -3815,12 +3815,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VOXR</t>
+          <t>TOP</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PMTW</t>
+          <t>PCTY</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -3829,132 +3829,180 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>TRLV</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PPC</t>
+          <t>PHOE</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>PLSE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>PLUN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>TWAV</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>PMN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>USDE</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>PMTS</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>USDEW</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>PMTW</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VGNT</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PRPO</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>VMET</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PRQR</t>
+          <t>PPC</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>VOGX</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>PRAA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>VOXR</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>WHK</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PSUS</t>
+          <t>PRHI</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>XXI</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PRLD</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -3964,7 +4012,7 @@
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -3974,7 +4022,7 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>PRPO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -3984,7 +4032,7 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>QTTB</t>
+          <t>PRQR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -3994,7 +4042,7 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>RBKB</t>
+          <t>PRTA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -4004,7 +4052,7 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>PRTS</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -4014,7 +4062,7 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PSUS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -4024,7 +4072,7 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -4034,7 +4082,7 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RELY</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -4044,7 +4092,7 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -4054,7 +4102,7 @@
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RMCO</t>
+          <t>QTTB</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -4064,7 +4112,7 @@
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="inlineStr">
         <is>
-          <t>RMTI</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -4074,7 +4122,7 @@
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -4084,7 +4132,7 @@
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RCEL</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -4094,7 +4142,7 @@
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -4104,7 +4152,7 @@
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="inlineStr">
         <is>
-          <t>RUM</t>
+          <t>RELY</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -4114,7 +4162,7 @@
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>RILYG</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -4124,7 +4172,7 @@
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>RMCO</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -4134,7 +4182,7 @@
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -4144,7 +4192,7 @@
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -4154,7 +4202,7 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -4164,7 +4212,7 @@
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>RRGB</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -4174,7 +4222,7 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>RUM</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -4184,7 +4232,7 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SENEA</t>
+          <t>RWAYI</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -4194,7 +4242,7 @@
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SHC</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -4204,7 +4252,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SAIH</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -4214,7 +4262,7 @@
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SLNG</t>
+          <t>SATL</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -4224,7 +4272,7 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>SAV</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -4234,7 +4282,7 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -4244,7 +4292,7 @@
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>SCTX</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -4254,7 +4302,7 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>SCYX</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -4264,7 +4312,7 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SPAI</t>
+          <t>SENEA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -4274,7 +4322,7 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SPCB</t>
+          <t>SHC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -4284,7 +4332,7 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SPEG</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -4294,7 +4342,7 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SLNG</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -4304,7 +4352,7 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>SLP</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -4314,7 +4362,7 @@
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -4324,7 +4372,7 @@
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>SMCIP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -4334,7 +4382,7 @@
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -4344,7 +4392,7 @@
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>TECX</t>
+          <t>SOPH</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -4354,7 +4402,7 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SPAI</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -4364,7 +4412,7 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>SPCB</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -4374,7 +4422,7 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>TKNO</t>
+          <t>SPEG</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -4384,7 +4432,7 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>SPSC</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -4394,7 +4442,7 @@
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SQFTP</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -4404,7 +4452,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>STEP</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -4414,7 +4462,7 @@
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>STRA</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -4424,7 +4472,7 @@
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>SUNC</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -4434,7 +4482,7 @@
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>VACI</t>
+          <t>TECX</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -4444,7 +4492,7 @@
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -4454,11 +4502,101 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>XRN</t>
+          <t>TILE</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>TKNO</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>TLF</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>TMDX</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>TRIN</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>VACI</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>XRN</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
